--- a/data.mn/public/datasets/mrpam-mining-permits.xlsx
+++ b/data.mn/public/datasets/mrpam-mining-permits.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC68"/>
+  <dimension ref="A1:EC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -28220,6 +28220,812 @@
         <v>50</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>26</v>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+      <c r="D69" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>21</v>
+      </c>
+      <c r="F69" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>32</v>
+      </c>
+      <c r="H69" t="n">
+        <v>454.8</v>
+      </c>
+      <c r="I69" t="n">
+        <v>90</v>
+      </c>
+      <c r="J69" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K69" t="n">
+        <v>31</v>
+      </c>
+      <c r="L69" t="n">
+        <v>475.1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>121</v>
+      </c>
+      <c r="N69" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="O69" t="n">
+        <v>56</v>
+      </c>
+      <c r="P69" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>99</v>
+      </c>
+      <c r="R69" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="S69" t="n">
+        <v>155</v>
+      </c>
+      <c r="T69" t="n">
+        <v>168</v>
+      </c>
+      <c r="U69" t="n">
+        <v>36</v>
+      </c>
+      <c r="V69" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>75</v>
+      </c>
+      <c r="X69" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>111</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>67</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>598.8</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>882.7</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>143</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>300.8</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>232</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>1183.5</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>375</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>61</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>135</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>519.9</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>196</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>604.7</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>88</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>54</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>683.8</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>142</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>17</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>210</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>98</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>137</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>272.1</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>235</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>84</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>38</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>122</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>20</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>22</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>5</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>9</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>14</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>39</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>127</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>166</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>41</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>74</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>115</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>91</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>301</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>392</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>93</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>95</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>45</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="DI69" t="n">
+        <v>111</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>852.8</v>
+      </c>
+      <c r="DK69" t="n">
+        <v>156</v>
+      </c>
+      <c r="DL69" t="n">
+        <v>226</v>
+      </c>
+      <c r="DM69" t="n">
+        <v>70</v>
+      </c>
+      <c r="DN69" t="n">
+        <v>27</v>
+      </c>
+      <c r="DO69" t="n">
+        <v>50</v>
+      </c>
+      <c r="DP69" t="n">
+        <v>253.1</v>
+      </c>
+      <c r="DQ69" t="n">
+        <v>120</v>
+      </c>
+      <c r="DR69" t="n">
+        <v>175.3</v>
+      </c>
+      <c r="DS69" t="n">
+        <v>35</v>
+      </c>
+      <c r="DT69" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="DU69" t="n">
+        <v>31</v>
+      </c>
+      <c r="DV69" t="n">
+        <v>199.4</v>
+      </c>
+      <c r="DW69" t="n">
+        <v>66</v>
+      </c>
+      <c r="DX69" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="DY69" t="n">
+        <v>36</v>
+      </c>
+      <c r="DZ69" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="EA69" t="n">
+        <v>14</v>
+      </c>
+      <c r="EB69" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="EC69" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>26</v>
+      </c>
+      <c r="C70" t="n">
+        <v>11</v>
+      </c>
+      <c r="D70" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>21</v>
+      </c>
+      <c r="F70" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>32</v>
+      </c>
+      <c r="H70" t="n">
+        <v>458.6</v>
+      </c>
+      <c r="I70" t="n">
+        <v>92</v>
+      </c>
+      <c r="J70" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>31</v>
+      </c>
+      <c r="L70" t="n">
+        <v>478.9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>123</v>
+      </c>
+      <c r="N70" t="n">
+        <v>329.1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>57</v>
+      </c>
+      <c r="P70" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>99</v>
+      </c>
+      <c r="R70" t="n">
+        <v>496.1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>156</v>
+      </c>
+      <c r="T70" t="n">
+        <v>168</v>
+      </c>
+      <c r="U70" t="n">
+        <v>36</v>
+      </c>
+      <c r="V70" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="W70" t="n">
+        <v>75</v>
+      </c>
+      <c r="X70" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>111</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>67</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>598.8</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>865.6</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>233</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>1168.4</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>373</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>61</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>135</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>519.9</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>196</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>604.7</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>88</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>54</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>683.8</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>142</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>17</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>97</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>137</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>272</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>234</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>84</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>38</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>420.4</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>122</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>20</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>22</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>5</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>9</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>14</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>39</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>127</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>166</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>41</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>74</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>115</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>89</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>304</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="CY70" t="n">
+        <v>393</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>93</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>95</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="DG70" t="n">
+        <v>45</v>
+      </c>
+      <c r="DH70" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="DI70" t="n">
+        <v>111</v>
+      </c>
+      <c r="DJ70" t="n">
+        <v>852.8</v>
+      </c>
+      <c r="DK70" t="n">
+        <v>156</v>
+      </c>
+      <c r="DL70" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="DM70" t="n">
+        <v>71</v>
+      </c>
+      <c r="DN70" t="n">
+        <v>27</v>
+      </c>
+      <c r="DO70" t="n">
+        <v>50</v>
+      </c>
+      <c r="DP70" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="DQ70" t="n">
+        <v>121</v>
+      </c>
+      <c r="DR70" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="DS70" t="n">
+        <v>36</v>
+      </c>
+      <c r="DT70" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="DU70" t="n">
+        <v>31</v>
+      </c>
+      <c r="DV70" t="n">
+        <v>202.4</v>
+      </c>
+      <c r="DW70" t="n">
+        <v>67</v>
+      </c>
+      <c r="DX70" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="DY70" t="n">
+        <v>36</v>
+      </c>
+      <c r="DZ70" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="EA70" t="n">
+        <v>14</v>
+      </c>
+      <c r="EB70" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="EC70" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28231,7 +29037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC68"/>
+  <dimension ref="A1:EC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -56037,6 +56843,812 @@
         <v>349</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>21</v>
+      </c>
+      <c r="C69" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>32</v>
+      </c>
+      <c r="F69" t="n">
+        <v>11</v>
+      </c>
+      <c r="G69" t="n">
+        <v>26</v>
+      </c>
+      <c r="H69" t="n">
+        <v>31</v>
+      </c>
+      <c r="I69" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>475.1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>121</v>
+      </c>
+      <c r="L69" t="n">
+        <v>90</v>
+      </c>
+      <c r="M69" t="n">
+        <v>454.8</v>
+      </c>
+      <c r="N69" t="n">
+        <v>99</v>
+      </c>
+      <c r="O69" t="n">
+        <v>167</v>
+      </c>
+      <c r="P69" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>155</v>
+      </c>
+      <c r="R69" t="n">
+        <v>56</v>
+      </c>
+      <c r="S69" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="T69" t="n">
+        <v>75</v>
+      </c>
+      <c r="U69" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>111</v>
+      </c>
+      <c r="X69" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>168</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>683.8</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>142</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>88</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>604.7</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>232</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>300.8</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1183.5</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>375</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>143</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>882.7</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>85</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>82</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>170</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>85</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>598.8</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>135</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>519.9</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>196</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>61</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>36</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>14</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>127</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>166</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>39</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>74</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>115</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>41</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>301</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>392</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>91</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>50</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>27</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>253.1</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>120</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>70</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>226</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>93</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>95</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>122</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>84</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>137</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>272.1</v>
+      </c>
+      <c r="DI69" t="n">
+        <v>235</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>98</v>
+      </c>
+      <c r="DK69" t="n">
+        <v>210</v>
+      </c>
+      <c r="DL69" t="n">
+        <v>20</v>
+      </c>
+      <c r="DM69" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="DN69" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="DO69" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP69" t="n">
+        <v>2</v>
+      </c>
+      <c r="DQ69" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="DR69" t="n">
+        <v>31</v>
+      </c>
+      <c r="DS69" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="DT69" t="n">
+        <v>199.4</v>
+      </c>
+      <c r="DU69" t="n">
+        <v>66</v>
+      </c>
+      <c r="DV69" t="n">
+        <v>35</v>
+      </c>
+      <c r="DW69" t="n">
+        <v>175.3</v>
+      </c>
+      <c r="DX69" t="n">
+        <v>111</v>
+      </c>
+      <c r="DY69" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="DZ69" t="n">
+        <v>852.8</v>
+      </c>
+      <c r="EA69" t="n">
+        <v>156</v>
+      </c>
+      <c r="EB69" t="n">
+        <v>45</v>
+      </c>
+      <c r="EC69" t="n">
+        <v>364.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>21</v>
+      </c>
+      <c r="C70" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D70" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>32</v>
+      </c>
+      <c r="F70" t="n">
+        <v>11</v>
+      </c>
+      <c r="G70" t="n">
+        <v>26</v>
+      </c>
+      <c r="H70" t="n">
+        <v>31</v>
+      </c>
+      <c r="I70" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>478.9</v>
+      </c>
+      <c r="K70" t="n">
+        <v>123</v>
+      </c>
+      <c r="L70" t="n">
+        <v>92</v>
+      </c>
+      <c r="M70" t="n">
+        <v>458.6</v>
+      </c>
+      <c r="N70" t="n">
+        <v>99</v>
+      </c>
+      <c r="O70" t="n">
+        <v>167</v>
+      </c>
+      <c r="P70" t="n">
+        <v>496.1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>156</v>
+      </c>
+      <c r="R70" t="n">
+        <v>57</v>
+      </c>
+      <c r="S70" t="n">
+        <v>329.1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>75</v>
+      </c>
+      <c r="U70" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="W70" t="n">
+        <v>111</v>
+      </c>
+      <c r="X70" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>168</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>683.8</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>142</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>88</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>604.7</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>233</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>302.8</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>1168.4</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>373</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>140</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>865.6</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>85</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>82</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>170</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>85</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>598.8</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>135</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>519.9</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>196</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>61</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>50</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>36</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>14</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>127</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>166</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>39</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>74</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>115</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>41</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>304</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>393</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>89</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>50</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>27</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>121</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>71</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>93</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>95</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY70" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>420.4</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>122</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>84</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>137</v>
+      </c>
+      <c r="DG70" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="DH70" t="n">
+        <v>272</v>
+      </c>
+      <c r="DI70" t="n">
+        <v>234</v>
+      </c>
+      <c r="DJ70" t="n">
+        <v>97</v>
+      </c>
+      <c r="DK70" t="n">
+        <v>204.6</v>
+      </c>
+      <c r="DL70" t="n">
+        <v>20</v>
+      </c>
+      <c r="DM70" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="DN70" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="DO70" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP70" t="n">
+        <v>2</v>
+      </c>
+      <c r="DQ70" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="DR70" t="n">
+        <v>31</v>
+      </c>
+      <c r="DS70" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="DT70" t="n">
+        <v>202.4</v>
+      </c>
+      <c r="DU70" t="n">
+        <v>67</v>
+      </c>
+      <c r="DV70" t="n">
+        <v>36</v>
+      </c>
+      <c r="DW70" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="DX70" t="n">
+        <v>111</v>
+      </c>
+      <c r="DY70" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="DZ70" t="n">
+        <v>852.8</v>
+      </c>
+      <c r="EA70" t="n">
+        <v>156</v>
+      </c>
+      <c r="EB70" t="n">
+        <v>45</v>
+      </c>
+      <c r="EC70" t="n">
+        <v>364.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
